--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AU$345</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AU$349</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14754" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14927" uniqueCount="1058">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:49:33+00:00</t>
+    <t>2026-06-18T12:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -430,7 +430,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -541,7 +541,7 @@
     <t>as-dr-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-practitioner|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-practitioner|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Practitioner.meta.security</t>
@@ -729,7 +729,7 @@
     <t>as-ext-registration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-registration|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-registration|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1035,7 +1035,7 @@
     <t>as-ext-frpractitioner-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1177,7 +1177,7 @@
     <t>as-ext-smartcard</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-smartcard|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-smartcard|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1311,7 +1311,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2281,7 +2281,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-1}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2345,7 +2345,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2503,7 +2503,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-1}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2741,7 +2741,7 @@
     <t>as-ext-education-level</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-education-level|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-education-level|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -3001,7 +3001,7 @@
     <t>Practitioner.qualification:degree.issuer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -3219,9 +3219,21 @@
     <t>Practitioner.qualification:attributionParticuliere.code</t>
   </si>
   <si>
+    <t>Practitioner.qualification:attributionParticuliere.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:attributionParticuliere.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:attributionParticuliere.code.coding</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J90-AttributionParticuliere-RASS/FHIR/JDV-J90-AttributionParticuliere-RASS|20200424120000</t>
   </si>
   <si>
+    <t>Practitioner.qualification:attributionParticuliere.code.text</t>
+  </si>
+  <si>
     <t>Practitioner.qualification:attributionParticuliere.period</t>
   </si>
   <si>
@@ -3249,7 +3261,7 @@
     <t>Practitioner.communication</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed|1.2.0-snapshot-1}
+    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -3591,7 +3603,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AU345"/>
+  <dimension ref="A1:AU349"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="82.7265625" customWidth="true" bestFit="true"/>
@@ -48968,11 +48980,13 @@
         <v>84</v>
       </c>
       <c r="X338" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y338" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="Y338" t="s" s="2">
+        <v>855</v>
+      </c>
       <c r="Z338" t="s" s="2">
-        <v>1035</v>
+        <v>856</v>
       </c>
       <c r="AA338" t="s" s="2">
         <v>84</v>
@@ -49038,12 +49052,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" hidden="true">
       <c r="A339" t="s" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>859</v>
+        <v>921</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" t="s" s="2">
@@ -49057,7 +49071,7 @@
         <v>102</v>
       </c>
       <c r="H339" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I339" t="s" s="2">
         <v>84</v>
@@ -49066,18 +49080,16 @@
         <v>84</v>
       </c>
       <c r="K339" t="s" s="2">
-        <v>271</v>
+        <v>116</v>
       </c>
       <c r="L339" t="s" s="2">
-        <v>860</v>
+        <v>117</v>
       </c>
       <c r="M339" t="s" s="2">
-        <v>861</v>
+        <v>118</v>
       </c>
       <c r="N339" s="2"/>
-      <c r="O339" t="s" s="2">
-        <v>862</v>
-      </c>
+      <c r="O339" s="2"/>
       <c r="P339" t="s" s="2">
         <v>84</v>
       </c>
@@ -49125,7 +49137,7 @@
         <v>84</v>
       </c>
       <c r="AF339" t="s" s="2">
-        <v>859</v>
+        <v>119</v>
       </c>
       <c r="AG339" t="s" s="2">
         <v>85</v>
@@ -49137,7 +49149,7 @@
         <v>84</v>
       </c>
       <c r="AJ339" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK339" t="s" s="2">
         <v>84</v>
@@ -49164,10 +49176,10 @@
         <v>84</v>
       </c>
       <c r="AS339" t="s" s="2">
-        <v>863</v>
+        <v>120</v>
       </c>
       <c r="AT339" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AU339" t="s" s="2">
         <v>84</v>
@@ -49175,21 +49187,21 @@
     </row>
     <row r="340" hidden="true">
       <c r="A340" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>951</v>
+        <v>923</v>
       </c>
       <c r="C340" s="2"/>
       <c r="D340" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E340" s="2"/>
       <c r="F340" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G340" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H340" t="s" s="2">
         <v>84</v>
@@ -49201,15 +49213,17 @@
         <v>84</v>
       </c>
       <c r="K340" t="s" s="2">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L340" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="M340" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N340" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="N340" t="s" s="2">
+        <v>126</v>
+      </c>
       <c r="O340" s="2"/>
       <c r="P340" t="s" s="2">
         <v>84</v>
@@ -49246,31 +49260,31 @@
         <v>84</v>
       </c>
       <c r="AB340" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC340" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD340" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE340" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF340" t="s" s="2">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="AG340" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH340" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI340" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ340" t="s" s="2">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="AK340" t="s" s="2">
         <v>84</v>
@@ -49308,14 +49322,14 @@
     </row>
     <row r="341" hidden="true">
       <c r="A341" t="s" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>953</v>
+        <v>925</v>
       </c>
       <c r="C341" s="2"/>
       <c r="D341" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E341" s="2"/>
       <c r="F341" t="s" s="2">
@@ -49331,21 +49345,23 @@
         <v>84</v>
       </c>
       <c r="J341" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K341" t="s" s="2">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="L341" t="s" s="2">
-        <v>124</v>
+        <v>926</v>
       </c>
       <c r="M341" t="s" s="2">
-        <v>125</v>
+        <v>927</v>
       </c>
       <c r="N341" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O341" s="2"/>
+        <v>928</v>
+      </c>
+      <c r="O341" t="s" s="2">
+        <v>929</v>
+      </c>
       <c r="P341" t="s" s="2">
         <v>84</v>
       </c>
@@ -49369,31 +49385,29 @@
         <v>84</v>
       </c>
       <c r="X341" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y341" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y341" s="2"/>
       <c r="Z341" t="s" s="2">
-        <v>84</v>
+        <v>1038</v>
       </c>
       <c r="AA341" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB341" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC341" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD341" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE341" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF341" t="s" s="2">
-        <v>130</v>
+        <v>931</v>
       </c>
       <c r="AG341" t="s" s="2">
         <v>85</v>
@@ -49405,7 +49419,7 @@
         <v>84</v>
       </c>
       <c r="AJ341" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK341" t="s" s="2">
         <v>84</v>
@@ -49429,10 +49443,10 @@
         <v>84</v>
       </c>
       <c r="AR341" t="s" s="2">
-        <v>84</v>
+        <v>932</v>
       </c>
       <c r="AS341" t="s" s="2">
-        <v>120</v>
+        <v>933</v>
       </c>
       <c r="AT341" t="s" s="2">
         <v>84</v>
@@ -49446,7 +49460,7 @@
         <v>1039</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>955</v>
+        <v>940</v>
       </c>
       <c r="C342" s="2"/>
       <c r="D342" t="s" s="2">
@@ -49469,18 +49483,20 @@
         <v>103</v>
       </c>
       <c r="K342" t="s" s="2">
-        <v>278</v>
+        <v>116</v>
       </c>
       <c r="L342" t="s" s="2">
-        <v>1040</v>
+        <v>941</v>
       </c>
       <c r="M342" t="s" s="2">
-        <v>280</v>
+        <v>942</v>
       </c>
       <c r="N342" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O342" s="2"/>
+        <v>943</v>
+      </c>
+      <c r="O342" t="s" s="2">
+        <v>944</v>
+      </c>
       <c r="P342" t="s" s="2">
         <v>84</v>
       </c>
@@ -49528,7 +49544,7 @@
         <v>84</v>
       </c>
       <c r="AF342" t="s" s="2">
-        <v>282</v>
+        <v>945</v>
       </c>
       <c r="AG342" t="s" s="2">
         <v>85</v>
@@ -49537,7 +49553,7 @@
         <v>102</v>
       </c>
       <c r="AI342" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ342" t="s" s="2">
         <v>114</v>
@@ -49564,10 +49580,10 @@
         <v>84</v>
       </c>
       <c r="AR342" t="s" s="2">
-        <v>285</v>
+        <v>946</v>
       </c>
       <c r="AS342" t="s" s="2">
-        <v>286</v>
+        <v>947</v>
       </c>
       <c r="AT342" t="s" s="2">
         <v>84</v>
@@ -49576,12 +49592,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="343" hidden="true">
+    <row r="343">
       <c r="A343" t="s" s="2">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>959</v>
+        <v>859</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" t="s" s="2">
@@ -49595,33 +49611,31 @@
         <v>102</v>
       </c>
       <c r="H343" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I343" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J343" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K343" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="L343" t="s" s="2">
-        <v>1042</v>
+        <v>860</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N343" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O343" s="2"/>
+        <v>861</v>
+      </c>
+      <c r="N343" s="2"/>
+      <c r="O343" t="s" s="2">
+        <v>862</v>
+      </c>
       <c r="P343" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q343" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="Q343" s="2"/>
       <c r="R343" t="s" s="2">
         <v>84</v>
       </c>
@@ -49665,7 +49679,7 @@
         <v>84</v>
       </c>
       <c r="AF343" t="s" s="2">
-        <v>293</v>
+        <v>859</v>
       </c>
       <c r="AG343" t="s" s="2">
         <v>85</v>
@@ -49674,7 +49688,7 @@
         <v>102</v>
       </c>
       <c r="AI343" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ343" t="s" s="2">
         <v>114</v>
@@ -49701,13 +49715,13 @@
         <v>84</v>
       </c>
       <c r="AR343" t="s" s="2">
-        <v>295</v>
+        <v>84</v>
       </c>
       <c r="AS343" t="s" s="2">
-        <v>296</v>
+        <v>863</v>
       </c>
       <c r="AT343" t="s" s="2">
-        <v>84</v>
+        <v>864</v>
       </c>
       <c r="AU343" t="s" s="2">
         <v>84</v>
@@ -49715,10 +49729,10 @@
     </row>
     <row r="344" hidden="true">
       <c r="A344" t="s" s="2">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>865</v>
+        <v>951</v>
       </c>
       <c r="C344" s="2"/>
       <c r="D344" t="s" s="2">
@@ -49741,13 +49755,13 @@
         <v>84</v>
       </c>
       <c r="K344" t="s" s="2">
-        <v>558</v>
+        <v>116</v>
       </c>
       <c r="L344" t="s" s="2">
-        <v>866</v>
+        <v>117</v>
       </c>
       <c r="M344" t="s" s="2">
-        <v>867</v>
+        <v>118</v>
       </c>
       <c r="N344" s="2"/>
       <c r="O344" s="2"/>
@@ -49798,7 +49812,7 @@
         <v>84</v>
       </c>
       <c r="AF344" t="s" s="2">
-        <v>865</v>
+        <v>119</v>
       </c>
       <c r="AG344" t="s" s="2">
         <v>85</v>
@@ -49810,7 +49824,7 @@
         <v>84</v>
       </c>
       <c r="AJ344" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK344" t="s" s="2">
         <v>84</v>
@@ -49837,7 +49851,7 @@
         <v>84</v>
       </c>
       <c r="AS344" t="s" s="2">
-        <v>868</v>
+        <v>120</v>
       </c>
       <c r="AT344" t="s" s="2">
         <v>84</v>
@@ -49846,16 +49860,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="345">
+    <row r="345" hidden="true">
       <c r="A345" t="s" s="2">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>1044</v>
+        <v>953</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E345" s="2"/>
       <c r="F345" t="s" s="2">
@@ -49865,7 +49879,7 @@
         <v>86</v>
       </c>
       <c r="H345" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I345" t="s" s="2">
         <v>84</v>
@@ -49874,20 +49888,18 @@
         <v>84</v>
       </c>
       <c r="K345" t="s" s="2">
-        <v>1045</v>
+        <v>123</v>
       </c>
       <c r="L345" t="s" s="2">
-        <v>1046</v>
+        <v>124</v>
       </c>
       <c r="M345" t="s" s="2">
-        <v>1047</v>
+        <v>125</v>
       </c>
       <c r="N345" t="s" s="2">
-        <v>1048</v>
-      </c>
-      <c r="O345" t="s" s="2">
-        <v>1049</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="O345" s="2"/>
       <c r="P345" t="s" s="2">
         <v>84</v>
       </c>
@@ -49911,29 +49923,31 @@
         <v>84</v>
       </c>
       <c r="X345" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y345" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y345" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z345" t="s" s="2">
-        <v>1050</v>
+        <v>84</v>
       </c>
       <c r="AA345" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB345" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC345" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD345" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE345" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF345" t="s" s="2">
-        <v>1044</v>
+        <v>130</v>
       </c>
       <c r="AG345" t="s" s="2">
         <v>85</v>
@@ -49945,44 +49959,584 @@
         <v>84</v>
       </c>
       <c r="AJ345" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK345" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL345" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM345" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN345" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO345" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP345" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ345" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR345" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS345" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AT345" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU345" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="346" hidden="true">
+      <c r="A346" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="B346" t="s" s="2">
+        <v>955</v>
+      </c>
+      <c r="C346" s="2"/>
+      <c r="D346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E346" s="2"/>
+      <c r="F346" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G346" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J346" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K346" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L346" t="s" s="2">
+        <v>1044</v>
+      </c>
+      <c r="M346" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N346" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O346" s="2"/>
+      <c r="P346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q346" s="2"/>
+      <c r="R346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF346" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG346" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH346" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI346" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AJ346" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AK345" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL345" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM345" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN345" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO345" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP345" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ345" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR345" t="s" s="2">
+      <c r="AK346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR346" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AS346" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AT346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU346" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="347" hidden="true">
+      <c r="A347" t="s" s="2">
+        <v>1045</v>
+      </c>
+      <c r="B347" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="C347" s="2"/>
+      <c r="D347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E347" s="2"/>
+      <c r="F347" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G347" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J347" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K347" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L347" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="M347" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N347" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O347" s="2"/>
+      <c r="P347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q347" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="R347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF347" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AG347" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH347" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI347" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AJ347" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR347" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AS347" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AT347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU347" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="348" hidden="true">
+      <c r="A348" t="s" s="2">
+        <v>1047</v>
+      </c>
+      <c r="B348" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="C348" s="2"/>
+      <c r="D348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E348" s="2"/>
+      <c r="F348" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G348" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K348" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L348" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="M348" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="N348" s="2"/>
+      <c r="O348" s="2"/>
+      <c r="P348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q348" s="2"/>
+      <c r="R348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF348" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="AG348" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH348" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ348" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS348" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="AT348" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU348" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s" s="2">
+        <v>1048</v>
+      </c>
+      <c r="B349" t="s" s="2">
+        <v>1048</v>
+      </c>
+      <c r="C349" s="2"/>
+      <c r="D349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E349" s="2"/>
+      <c r="F349" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G349" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H349" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K349" t="s" s="2">
+        <v>1049</v>
+      </c>
+      <c r="L349" t="s" s="2">
+        <v>1050</v>
+      </c>
+      <c r="M349" t="s" s="2">
         <v>1051</v>
       </c>
-      <c r="AS345" t="s" s="2">
+      <c r="N349" t="s" s="2">
         <v>1052</v>
       </c>
-      <c r="AT345" t="s" s="2">
+      <c r="O349" t="s" s="2">
         <v>1053</v>
       </c>
-      <c r="AU345" t="s" s="2">
+      <c r="P349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q349" s="2"/>
+      <c r="R349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X349" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="Y349" s="2"/>
+      <c r="Z349" t="s" s="2">
+        <v>1054</v>
+      </c>
+      <c r="AA349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF349" t="s" s="2">
+        <v>1048</v>
+      </c>
+      <c r="AG349" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH349" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ349" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR349" t="s" s="2">
+        <v>1055</v>
+      </c>
+      <c r="AS349" t="s" s="2">
+        <v>1056</v>
+      </c>
+      <c r="AT349" t="s" s="2">
+        <v>1057</v>
+      </c>
+      <c r="AU349" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU345">
+  <autoFilter ref="A1:AU349">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -49992,7 +50546,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI344">
+  <conditionalFormatting sqref="A2:AI348">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:07:50+00:00</t>
+    <t>2026-06-18T13:08:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:08:38+00:00</t>
+    <t>2026-06-18T13:31:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
